--- a/data/trans_camb/IP19C03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Edad-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 74,5</t>
+          <t>14,91; 73,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 49,43</t>
+          <t>7,06; 46,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 5,32</t>
+          <t>-9,26; 5,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 13,42</t>
+          <t>-4,69; 13,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 15,99</t>
+          <t>-1,86; 16,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 14,01</t>
+          <t>-3,0; 13,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 13,37</t>
+          <t>-3,59; 13,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 18,93</t>
+          <t>1,62; 19,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 7,53</t>
+          <t>-4,27; 6,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 10,53</t>
+          <t>-1,35; 10,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 15,48</t>
+          <t>1,47; 14,26</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,77; 77,57</t>
+          <t>-62,76; 94,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 176,82</t>
+          <t>-35,65; 176,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 206,47</t>
+          <t>-13,49; 208,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 264,61</t>
+          <t>-27,86; 246,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 252,77</t>
+          <t>-29,68; 234,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 354,84</t>
+          <t>9,71; 370,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 107,95</t>
+          <t>-34,01; 88,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 141,72</t>
+          <t>-11,12; 136,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,08; 208,2</t>
+          <t>8,52; 182,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 9,61</t>
+          <t>-7,75; 9,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 2,69</t>
+          <t>-12,37; 2,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 11,05</t>
+          <t>-8,77; 10,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 10,84</t>
+          <t>-5,28; 10,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 7,3</t>
+          <t>-8,65; 6,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 9,61</t>
+          <t>-7,5; 8,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 7,54</t>
+          <t>-3,74; 8,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 3,77</t>
+          <t>-8,31; 2,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 6,97</t>
+          <t>-5,83; 7,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,21; 63,22</t>
+          <t>-32,05; 61,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,05; 19,4</t>
+          <t>-51,11; 19,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 66,65</t>
+          <t>-36,71; 73,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 92,15</t>
+          <t>-26,76; 87,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 59,6</t>
+          <t>-40,34; 56,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 79,31</t>
+          <t>-34,94; 73,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 50,74</t>
+          <t>-18,49; 57,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 25,79</t>
+          <t>-38,0; 19,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 46,41</t>
+          <t>-27,53; 51,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 8,5</t>
+          <t>-7,66; 8,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 1,03</t>
+          <t>-14,4; 0,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -4,61</t>
+          <t>-18,63; -4,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 8,19</t>
+          <t>-6,11; 8,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 8,7</t>
+          <t>-7,06; 8,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 0,05</t>
+          <t>-14,7; -0,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 6,47</t>
+          <t>-4,61; 6,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 2,65</t>
+          <t>-8,04; 2,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,91; -4,38</t>
+          <t>-13,81; -3,98</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 38,98</t>
+          <t>-24,99; 39,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,35; 4,8</t>
+          <t>-47,79; 1,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,58; -19,64</t>
+          <t>-60,51; -18,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,28; 43,14</t>
+          <t>-24,47; 47,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 46,32</t>
+          <t>-26,84; 47,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,68; 0,84</t>
+          <t>-55,25; 0,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 30,18</t>
+          <t>-16,68; 29,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 12,22</t>
+          <t>-30,96; 12,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,18; -18,95</t>
+          <t>-51,44; -17,55</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 5,29</t>
+          <t>-5,18; 4,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 1,02</t>
+          <t>-8,46; 0,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 1,33</t>
+          <t>-7,82; 1,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 6,51</t>
+          <t>-2,76; 6,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,66</t>
+          <t>-4,12; 5,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 3,86</t>
+          <t>-5,36; 3,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 4,12</t>
+          <t>-2,45; 4,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 1,81</t>
+          <t>-4,86; 2,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,9</t>
+          <t>-5,62; 1,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 29,39</t>
+          <t>-22,41; 23,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 6,31</t>
+          <t>-36,81; 3,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,46; 6,82</t>
+          <t>-34,09; 10,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 43,07</t>
+          <t>-14,58; 42,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 29,7</t>
+          <t>-21,09; 32,55</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 25,27</t>
+          <t>-27,76; 24,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 24,06</t>
+          <t>-12,37; 25,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 10,4</t>
+          <t>-23,22; 12,21</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 5,49</t>
+          <t>-27,12; 7,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Edad-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 73,68</t>
+          <t>14,03; 74,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 46,45</t>
+          <t>6,96; 50,86</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 5,91</t>
+          <t>-10,03; 5,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 13,6</t>
+          <t>-4,6; 13,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 16,03</t>
+          <t>-3,24; 15,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 13,36</t>
+          <t>-2,94; 12,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 13,03</t>
+          <t>-3,13; 11,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 19,15</t>
+          <t>0,75; 19,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 6,86</t>
+          <t>-4,58; 7,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 10,56</t>
+          <t>-1,89; 10,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 14,26</t>
+          <t>1,06; 14,86</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,76; 94,96</t>
+          <t>-66,2; 79,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,65; 176,41</t>
+          <t>-33,63; 178,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 208,65</t>
+          <t>-22,23; 205,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 246,3</t>
+          <t>-31,07; 222,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 234,48</t>
+          <t>-27,55; 211,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,71; 370,51</t>
+          <t>1,08; 321,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 88,68</t>
+          <t>-33,44; 97,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 136,94</t>
+          <t>-14,29; 138,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,52; 182,09</t>
+          <t>6,78; 194,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 9,0</t>
+          <t>-8,5; 10,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 2,88</t>
+          <t>-12,47; 3,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 10,45</t>
+          <t>-8,23; 12,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 10,64</t>
+          <t>-4,58; 11,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 6,9</t>
+          <t>-7,51; 8,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 8,68</t>
+          <t>-7,26; 8,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 8,4</t>
+          <t>-4,16; 7,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 2,7</t>
+          <t>-7,79; 3,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 7,53</t>
+          <t>-5,83; 6,35</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 61,9</t>
+          <t>-35,89; 67,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 19,03</t>
+          <t>-50,84; 22,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 73,54</t>
+          <t>-35,25; 78,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,76; 87,2</t>
+          <t>-23,06; 88,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,34; 56,57</t>
+          <t>-35,75; 67,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,94; 73,32</t>
+          <t>-34,75; 74,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 57,77</t>
+          <t>-19,3; 52,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,0; 19,7</t>
+          <t>-35,54; 23,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 51,99</t>
+          <t>-28,65; 42,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 8,85</t>
+          <t>-8,05; 8,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 0,54</t>
+          <t>-15,09; 0,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,63; -4,28</t>
+          <t>-18,4; -4,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 8,89</t>
+          <t>-7,33; 8,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 8,6</t>
+          <t>-7,15; 8,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,7; -0,14</t>
+          <t>-13,55; 0,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 6,1</t>
+          <t>-4,86; 5,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 2,94</t>
+          <t>-8,49; 2,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,81; -3,98</t>
+          <t>-14,18; -4,67</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 39,13</t>
+          <t>-25,94; 35,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,79; 1,89</t>
+          <t>-48,55; 3,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,51; -18,84</t>
+          <t>-59,59; -20,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 47,83</t>
+          <t>-27,54; 47,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 47,24</t>
+          <t>-28,45; 45,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,25; 0,34</t>
+          <t>-52,93; 0,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 29,04</t>
+          <t>-18,23; 26,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,96; 12,66</t>
+          <t>-31,12; 11,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,44; -17,55</t>
+          <t>-52,12; -19,99</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 4,42</t>
+          <t>-5,39; 4,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 0,81</t>
+          <t>-8,42; 0,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 1,89</t>
+          <t>-8,06; 1,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 6,56</t>
+          <t>-2,7; 7,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 5,02</t>
+          <t>-3,96; 5,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,73</t>
+          <t>-6,16; 3,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 4,37</t>
+          <t>-2,59; 3,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 2,08</t>
+          <t>-4,9; 1,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,28</t>
+          <t>-5,36; 1,14</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 23,74</t>
+          <t>-23,18; 23,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 3,98</t>
+          <t>-36,93; 4,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,09; 10,73</t>
+          <t>-35,53; 9,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 42,17</t>
+          <t>-13,5; 46,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 32,55</t>
+          <t>-19,48; 35,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 24,09</t>
+          <t>-30,57; 21,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 25,28</t>
+          <t>-12,0; 22,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 12,21</t>
+          <t>-23,47; 9,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 7,02</t>
+          <t>-25,74; 6,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41,77</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,22 +649,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>37,25</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21,79</t>
+          <t>21,05</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,03; 74,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>12,03; 71,53</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 50,86</t>
+          <t>6,48; 49,0</t>
         </is>
       </c>
     </row>
@@ -740,22 +740,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10,51</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,29</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,64</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,8</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,33</t>
+          <t>7,58</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>9,03</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 5,4</t>
+          <t>-2,84; 14,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 13,36</t>
+          <t>-3,16; 13,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 15,88</t>
+          <t>1,7; 20,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 12,44</t>
+          <t>-9,96; 5,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 11,81</t>
+          <t>-4,61; 13,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 19,2</t>
+          <t>-2,44; 17,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 7,12</t>
+          <t>-3,75; 7,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 10,35</t>
+          <t>-1,3; 10,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 14,86</t>
+          <t>3,15; 16,45</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53,08%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>116,29%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-19,87%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>33,89%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>57,69%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>52,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>53,08%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>103,25%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>87,62%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-66,2; 79,06</t>
+          <t>-25,91; 264,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 178,72</t>
+          <t>-28,06; 252,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 205,3</t>
+          <t>7,46; 393,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 222,48</t>
+          <t>-62,77; 77,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,55; 211,52</t>
+          <t>-34,74; 176,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 321,99</t>
+          <t>-16,68; 219,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 97,36</t>
+          <t>-29,57; 107,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 138,28</t>
+          <t>-11,09; 141,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 194,83</t>
+          <t>23,72; 222,8</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,65</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,36</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,39</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,69</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,65</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>-1,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 10,04</t>
+          <t>-5,82; 10,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 3,05</t>
+          <t>-8,29; 7,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 12,01</t>
+          <t>-8,49; 8,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 11,01</t>
+          <t>-7,28; 9,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 8,28</t>
+          <t>-12,35; 2,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 8,78</t>
+          <t>-9,84; 6,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 7,78</t>
+          <t>-3,7; 7,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 3,28</t>
+          <t>-8,39; 3,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 6,35</t>
+          <t>-7,04; 5,01</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15,89%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-2,18%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-3,92%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>7,07%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-23,81%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>15,89%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-2,18%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>-6,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>-5,8%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,89; 67,99</t>
+          <t>-28,55; 92,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 22,18</t>
+          <t>-37,88; 59,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,25; 78,76</t>
+          <t>-41,63; 70,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 88,78</t>
+          <t>-31,21; 63,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 67,04</t>
+          <t>-51,05; 19,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 74,13</t>
+          <t>-40,87; 45,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 52,79</t>
+          <t>-18,11; 50,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,54; 23,95</t>
+          <t>-38,87; 25,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 42,56</t>
+          <t>-34,0; 33,51</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,85</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-7,32</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,09</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-6,79</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-11,58</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,85</t>
+          <t>-11,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-9,13</t>
+          <t>-9,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 8,28</t>
+          <t>-6,72; 8,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 0,68</t>
+          <t>-6,82; 8,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,4; -4,83</t>
+          <t>-14,26; -0,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 8,36</t>
+          <t>-7,42; 8,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 8,76</t>
+          <t>-15,4; 1,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 0,23</t>
+          <t>-19,08; -4,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 5,77</t>
+          <t>-5,28; 6,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 2,42</t>
+          <t>-8,32; 2,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -4,67</t>
+          <t>-14,25; -4,74</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-32,97%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-25,5%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-43,48%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-30,86%</t>
+          <t>-44,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-37,52%</t>
+          <t>-38,91%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 35,91</t>
+          <t>-27,28; 43,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 3,27</t>
+          <t>-27,38; 46,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,59; -20,88</t>
+          <t>-55,23; -1,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 47,32</t>
+          <t>-24,58; 38,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 45,66</t>
+          <t>-49,35; 4,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,93; 0,99</t>
+          <t>-61,78; -20,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 26,08</t>
+          <t>-19,19; 30,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 11,06</t>
+          <t>-31,24; 12,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,12; -19,99</t>
+          <t>-52,62; -20,56</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,74</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-3,75</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,15</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-3,76</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-2,77</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 4,39</t>
+          <t>-3,23; 6,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 0,92</t>
+          <t>-3,74; 4,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 1,81</t>
+          <t>-6,02; 3,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 7,02</t>
+          <t>-5,0; 5,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 5,37</t>
+          <t>-8,38; 1,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 3,24</t>
+          <t>-8,51; 0,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 3,94</t>
+          <t>-2,32; 4,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 1,66</t>
+          <t>-4,76; 1,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 1,14</t>
+          <t>-6,04; 0,48</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-9,93%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-0,47%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-18,06%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-15,17%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-7,31%</t>
+          <t>-18,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-11,83%</t>
+          <t>-14,49%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 23,69</t>
+          <t>-16,11; 43,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 4,65</t>
+          <t>-18,81; 29,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 9,96</t>
+          <t>-30,54; 22,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 46,38</t>
+          <t>-22,88; 29,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 35,17</t>
+          <t>-35,96; 6,31</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 21,27</t>
+          <t>-36,3; 3,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 22,23</t>
+          <t>-11,1; 24,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 9,37</t>
+          <t>-22,96; 10,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 6,74</t>
+          <t>-29,06; 3,04</t>
         </is>
       </c>
     </row>
